--- a/01_test_base/Подборки для тестов.xlsx
+++ b/01_test_base/Подборки для тестов.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="39">
   <si>
     <t xml:space="preserve">Содержимое</t>
   </si>
@@ -107,6 +107,9 @@
     <t xml:space="preserve">Категория</t>
   </si>
   <si>
+    <t xml:space="preserve">Женский</t>
+  </si>
+  <si>
     <t xml:space="preserve">Лучшее средство без канцерогенов</t>
   </si>
   <si>
@@ -118,6 +121,9 @@
 «Средство_5» : «ALTEREGO ITALY Curego Hydraday»,
 «Средство_6» : «ALTEREGO ITALY Curego Hydraday»
 }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Уход за кожей лица</t>
   </si>
   <si>
     <t xml:space="preserve">Лучшая пара</t>
@@ -444,7 +450,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K1048576"/>
-  <sheetFormatPr defaultColWidth="12.19140625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.2265625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.94"/>
@@ -570,7 +576,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K1048576"/>
-  <sheetFormatPr defaultColWidth="12.01953125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.0546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.94"/>
@@ -623,7 +629,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C2" s="6" t="n">
         <v>32</v>
@@ -652,7 +658,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>32</v>
@@ -664,13 +670,13 @@
         <v>14</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>16</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I3" s="6"/>
       <c r="J3" s="10"/>
@@ -678,10 +684,10 @@
     </row>
     <row r="4" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>32</v>
@@ -705,12 +711,12 @@
       <c r="J4" s="9"/>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="307.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="292.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>32</v>
@@ -722,13 +728,13 @@
         <v>20</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>16</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I5" s="6"/>
       <c r="J5" s="9"/>
@@ -736,42 +742,42 @@
     </row>
     <row r="6" customFormat="false" ht="95.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F6" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="201.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F7" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="48.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F8" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="95.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F9" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="95.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F10" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/01_test_base/Подборки для тестов.xlsx
+++ b/01_test_base/Подборки для тестов.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Подборки" sheetId="1" state="visible" r:id="rId2"/>
@@ -21,11 +21,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="43">
   <si>
     <t xml:space="preserve">Содержимое</t>
   </si>
   <si>
+    <t xml:space="preserve">Группа</t>
+  </si>
+  <si>
     <t xml:space="preserve">Пол</t>
   </si>
   <si>
@@ -47,16 +50,16 @@
     <t xml:space="preserve">Средства</t>
   </si>
   <si>
-    <t xml:space="preserve">Лучший вариант</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Итог</t>
+    <t xml:space="preserve">Путь</t>
   </si>
   <si>
     <t xml:space="preserve">Хеш</t>
   </si>
   <si>
     <t xml:space="preserve">Шампуни</t>
+  </si>
+  <si>
+    <t xml:space="preserve">платная</t>
   </si>
   <si>
     <t xml:space="preserve">женский</t>
@@ -87,6 +90,9 @@
     <t xml:space="preserve">уход за кожей лица</t>
   </si>
   <si>
+    <t xml:space="preserve">бесплатная</t>
+  </si>
+  <si>
     <t xml:space="preserve">КЛ1</t>
   </si>
   <si>
@@ -105,6 +111,12 @@
   </si>
   <si>
     <t xml:space="preserve">Категория</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Лучший вариант</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Итог</t>
   </si>
   <si>
     <t xml:space="preserve">Женский</t>
@@ -450,15 +462,14 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K1048576"/>
-  <sheetFormatPr defaultColWidth="12.2265625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.23828125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="15.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="19.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="56.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="16.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="15.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="19.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="56.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="44.02"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="29.25"/>
   </cols>
@@ -467,7 +478,7 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
@@ -502,14 +513,14 @@
       <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="6" t="n">
         <v>32</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>13</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>14</v>
@@ -520,42 +531,46 @@
       <c r="G2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="6"/>
+      <c r="I2" s="7" t="s">
+        <v>18</v>
+      </c>
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>19</v>
-      </c>
       <c r="E3" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="6"/>
+        <v>23</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>24</v>
+      </c>
       <c r="J3" s="8"/>
       <c r="K3" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -576,7 +591,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K1048576"/>
-  <sheetFormatPr defaultColWidth="12.0546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.07421875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.94"/>
@@ -591,34 +606,34 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>10</v>
@@ -629,25 +644,25 @@
         <v>11</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C2" s="6" t="n">
         <v>32</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" s="6"/>
       <c r="J2" s="9"/>
@@ -658,25 +673,25 @@
         <v>11</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>32</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I3" s="6"/>
       <c r="J3" s="10"/>
@@ -684,28 +699,28 @@
     </row>
     <row r="4" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>32</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I4" s="6"/>
       <c r="J4" s="9"/>
@@ -713,28 +728,28 @@
     </row>
     <row r="5" customFormat="false" ht="292.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>32</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I5" s="6"/>
       <c r="J5" s="9"/>
@@ -742,42 +757,42 @@
     </row>
     <row r="6" customFormat="false" ht="95.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F6" s="11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="201.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F7" s="11" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="48.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F8" s="11" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="95.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F9" s="11" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="95.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F10" s="11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
